--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>1</v>
